--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260717_204458.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260717_204458.xlsx
@@ -5902,7 +5902,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6358,7 +6358,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6434,7 +6434,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -8706,7 +8706,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8782,7 +8782,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8858,7 +8858,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260717_204458.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260717_204458.xlsx
@@ -5902,7 +5902,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6358,7 +6358,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6434,7 +6434,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260717_204458.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260717_204458.xlsx
@@ -5902,7 +5902,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6358,7 +6358,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6434,7 +6434,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -8706,7 +8706,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8782,7 +8782,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8858,7 +8858,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260717_204458.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260717_204458.xlsx
@@ -5902,7 +5902,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6358,7 +6358,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6434,7 +6434,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6652,7 +6652,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6952,7 +6952,7 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7178,7 +7178,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7330,7 +7330,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -8706,7 +8706,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8782,7 +8782,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8858,7 +8858,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
